--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 07:10</t>
+          <t>Generated: 2026-06-04 07:16</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127664671063958</v>
+        <v>0.1127788171159506</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08439083118371769</v>
+        <v>0.0844007811999028</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746439476463948</v>
+        <v>0.0746521225364157</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1212339611865206</v>
+        <v>0.1212451642333992</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.095279278882744</v>
+        <v>0.0952897137224155</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689785347176748</v>
+        <v>0.0689783678453408</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09595712435816429</v>
+        <v>0.09596048915885461</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682589072996488</v>
+        <v>0.0682639501572225</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0937124167612285</v>
+        <v>0.09362979868343391</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0830663475100475</v>
+        <v>0.08307633602336</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.050658604297883</v>
+        <v>0.0506641523500936</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510535790495797</v>
+        <v>0.0510603069736102</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.121228819959059</v>
+        <v>0.1127664671063958</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1212339611865206</v>
+        <v>0.1127788171159506</v>
       </c>
       <c r="D4" t="n">
-        <v>5.14122746160528e-06</v>
+        <v>1.23500095547957e-05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.112762644153064</v>
+        <v>0.1212339611865206</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1127664671063958</v>
+        <v>0.1212451642333992</v>
       </c>
       <c r="D5" t="n">
-        <v>3.822953331802936e-06</v>
+        <v>1.120304687859952e-05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09527604877147069</v>
+        <v>0.095279278882744</v>
       </c>
       <c r="C6" t="n">
-        <v>0.095279278882744</v>
+        <v>0.0952897137224155</v>
       </c>
       <c r="D6" t="n">
-        <v>3.230111273302972e-06</v>
+        <v>1.04348396715026e-05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09370923976894451</v>
+        <v>0.0830663475100475</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0937124167612285</v>
+        <v>0.08307633602336</v>
       </c>
       <c r="D7" t="n">
-        <v>3.176992283998592e-06</v>
+        <v>9.988513312492175e-06</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0830635308846582</v>
+        <v>0.08439083118371769</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0830663475100475</v>
+        <v>0.0844007811999028</v>
       </c>
       <c r="D8" t="n">
-        <v>2.81662538929861e-06</v>
+        <v>9.950016185103494e-06</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0682562604833452</v>
+        <v>0.0746439476463948</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0682589072996488</v>
+        <v>0.0746521225364157</v>
       </c>
       <c r="D9" t="n">
-        <v>2.646816303603083e-06</v>
+        <v>8.17489002090388e-06</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0746414171039767</v>
+        <v>0.0510535790495797</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0746439476463948</v>
+        <v>0.0510603069736102</v>
       </c>
       <c r="D10" t="n">
-        <v>2.530542418097137e-06</v>
+        <v>6.727924030495991e-06</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0510518482562407</v>
+        <v>0.050658604297883</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0510535790495797</v>
+        <v>0.0506641523500936</v>
       </c>
       <c r="D11" t="n">
-        <v>1.730793339004e-06</v>
+        <v>5.548052210598009e-06</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0506568868947839</v>
+        <v>0.0682589072996488</v>
       </c>
       <c r="C12" t="n">
-        <v>0.050658604297883</v>
+        <v>0.0682639501572225</v>
       </c>
       <c r="D12" t="n">
-        <v>1.717403099101011e-06</v>
+        <v>5.042857573703263e-06</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0843945627099358</v>
+        <v>0.09595712435816429</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08439083118371769</v>
+        <v>0.09596048915885461</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.731526218103687e-06</v>
+        <v>3.36480069031142e-06</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0689822939665688</v>
+        <v>0.0689785347176748</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0689785347176748</v>
+        <v>0.0689783678453408</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.759248893994704e-06</v>
+        <v>-1.668723340064737e-07</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0959764470479519</v>
+        <v>0.0937124167612285</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09595712435816429</v>
+        <v>0.09362979868343391</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.932268978760421e-05</v>
+        <v>-8.261807779459673e-05</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3179,19 +3179,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>197.27</v>
+        <v>197.78</v>
       </c>
       <c r="C5" t="n">
-        <v>132.16</v>
+        <v>132.18</v>
       </c>
       <c r="D5" t="n">
         <v>10.35</v>
       </c>
       <c r="E5" t="n">
-        <v>166.21</v>
+        <v>166.72</v>
       </c>
       <c r="F5" t="n">
-        <v>167.68</v>
+        <v>168.11</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10143.5</v>
+        <v>10146.5</v>
       </c>
       <c r="C7" t="n">
-        <v>8887.620000000001</v>
+        <v>8887.74</v>
       </c>
       <c r="D7" t="n">
         <v>337.75</v>
       </c>
       <c r="E7" t="n">
-        <v>9130.25</v>
+        <v>9133.25</v>
       </c>
       <c r="F7" t="n">
-        <v>8621.98</v>
+        <v>8624.52</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3307,19 +3307,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136.2</v>
+        <v>136.45</v>
       </c>
       <c r="C9" t="n">
-        <v>104.98</v>
+        <v>104.99</v>
       </c>
       <c r="D9" t="n">
         <v>8.01</v>
       </c>
       <c r="E9" t="n">
-        <v>112.16</v>
+        <v>112.41</v>
       </c>
       <c r="F9" t="n">
-        <v>115.77</v>
+        <v>115.98</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1303.1</v>
+        <v>1303.7</v>
       </c>
       <c r="C10" t="n">
-        <v>958.29</v>
+        <v>958.3200000000001</v>
       </c>
       <c r="D10" t="n">
         <v>53.63</v>
       </c>
       <c r="E10" t="n">
-        <v>1142.22</v>
+        <v>1142.82</v>
       </c>
       <c r="F10" t="n">
-        <v>1107.63</v>
+        <v>1108.14</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>231.6</v>
+        <v>231.1</v>
       </c>
       <c r="C11" t="n">
-        <v>209.32</v>
+        <v>209.3</v>
       </c>
       <c r="D11" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>204.69</v>
+        <v>204.19</v>
       </c>
       <c r="F11" t="n">
-        <v>196.86</v>
+        <v>196.44</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,19 +3403,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.73</v>
+        <v>20.95</v>
       </c>
       <c r="C12" t="n">
-        <v>17.48</v>
+        <v>17.49</v>
       </c>
       <c r="D12" t="n">
         <v>1.1</v>
       </c>
       <c r="E12" t="n">
-        <v>17.43</v>
+        <v>17.65</v>
       </c>
       <c r="F12" t="n">
-        <v>17.62</v>
+        <v>17.81</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>526.9</v>
+        <v>526.8</v>
       </c>
       <c r="C13" t="n">
         <v>463.12</v>
@@ -3444,10 +3444,10 @@
         <v>24.97</v>
       </c>
       <c r="E13" t="n">
-        <v>452</v>
+        <v>451.9</v>
       </c>
       <c r="F13" t="n">
-        <v>447.87</v>
+        <v>447.78</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264.85</v>
+        <v>264.15</v>
       </c>
       <c r="C15" t="n">
-        <v>237.43</v>
+        <v>237.4</v>
       </c>
       <c r="D15" t="n">
         <v>15.97</v>
       </c>
       <c r="E15" t="n">
-        <v>216.93</v>
+        <v>216.23</v>
       </c>
       <c r="F15" t="n">
-        <v>225.12</v>
+        <v>224.53</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 07:16</t>
+          <t>Generated: 2026-06-04 08:12</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127788171159506</v>
+        <v>0.1127832209736098</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0844007811999028</v>
+        <v>0.0844118651575632</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746521225364157</v>
+        <v>0.0746550375991023</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1212451642333992</v>
+        <v>0.121255661517973</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0952897137224155</v>
+        <v>0.0952934346546469</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689783678453408</v>
+        <v>0.06894726286613161</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09596048915885461</v>
+        <v>0.0959678292115399</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682639501572225</v>
+        <v>0.06826258741533579</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09362979868343391</v>
+        <v>0.09360827560054941</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08307633602336</v>
+        <v>0.08309255094566879</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506641523500936</v>
+        <v>0.0506661307155445</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510603069736102</v>
+        <v>0.0510561433423345</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127664671063958</v>
+        <v>0.08307633602336</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1127788171159506</v>
+        <v>0.08309255094566879</v>
       </c>
       <c r="D4" t="n">
-        <v>1.23500095547957e-05</v>
+        <v>1.621492230879928e-05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1212339611865206</v>
+        <v>0.0844007811999028</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1212451642333992</v>
+        <v>0.0844118651575632</v>
       </c>
       <c r="D5" t="n">
-        <v>1.120304687859952e-05</v>
+        <v>1.108395766040438e-05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.095279278882744</v>
+        <v>0.1212451642333992</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0952897137224155</v>
+        <v>0.121255661517973</v>
       </c>
       <c r="D6" t="n">
-        <v>1.04348396715026e-05</v>
+        <v>1.049728457379329e-05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0830663475100475</v>
+        <v>0.09596048915885461</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08307633602336</v>
+        <v>0.0959678292115399</v>
       </c>
       <c r="D7" t="n">
-        <v>9.988513312492175e-06</v>
+        <v>7.34005268529514e-06</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08439083118371769</v>
+        <v>0.1127788171159506</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0844007811999028</v>
+        <v>0.1127832209736098</v>
       </c>
       <c r="D8" t="n">
-        <v>9.950016185103494e-06</v>
+        <v>4.403857659193711e-06</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0746439476463948</v>
+        <v>0.0952897137224155</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0746521225364157</v>
+        <v>0.0952934346546469</v>
       </c>
       <c r="D9" t="n">
-        <v>8.17489002090388e-06</v>
+        <v>3.720932231401908e-06</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0510535790495797</v>
+        <v>0.0746521225364157</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0510603069736102</v>
+        <v>0.0746550375991023</v>
       </c>
       <c r="D10" t="n">
-        <v>6.727924030495991e-06</v>
+        <v>2.915062686598135e-06</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.050658604297883</v>
+        <v>0.0506641523500936</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0506641523500936</v>
+        <v>0.0506661307155445</v>
       </c>
       <c r="D11" t="n">
-        <v>5.548052210598009e-06</v>
+        <v>1.978365450905351e-06</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0682589072996488</v>
+        <v>0.0682639501572225</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0682639501572225</v>
+        <v>0.06826258741533579</v>
       </c>
       <c r="D12" t="n">
-        <v>5.042857573703263e-06</v>
+        <v>-1.362741886709595e-06</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09595712435816429</v>
+        <v>0.0510603069736102</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09596048915885461</v>
+        <v>0.0510561433423345</v>
       </c>
       <c r="D13" t="n">
-        <v>3.36480069031142e-06</v>
+        <v>-4.163631275699853e-06</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0689785347176748</v>
+        <v>0.09362979868343391</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0689783678453408</v>
+        <v>0.09360827560054941</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.668723340064737e-07</v>
+        <v>-2.152308288450033e-05</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0937124167612285</v>
+        <v>0.0689783678453408</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09362979868343391</v>
+        <v>0.06894726286613161</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.261807779459673e-05</v>
+        <v>-3.110497920918998e-05</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3179,19 +3179,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>197.78</v>
+        <v>200.96</v>
       </c>
       <c r="C5" t="n">
-        <v>132.18</v>
+        <v>132.3</v>
       </c>
       <c r="D5" t="n">
         <v>10.35</v>
       </c>
       <c r="E5" t="n">
-        <v>166.72</v>
+        <v>169.9</v>
       </c>
       <c r="F5" t="n">
-        <v>168.11</v>
+        <v>170.82</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10146.5</v>
+        <v>10135.5</v>
       </c>
       <c r="C7" t="n">
-        <v>8887.74</v>
+        <v>8887.299999999999</v>
       </c>
       <c r="D7" t="n">
         <v>337.75</v>
       </c>
       <c r="E7" t="n">
-        <v>9133.25</v>
+        <v>9122.25</v>
       </c>
       <c r="F7" t="n">
-        <v>8624.52</v>
+        <v>8615.17</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3307,19 +3307,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136.45</v>
+        <v>137.1</v>
       </c>
       <c r="C9" t="n">
-        <v>104.99</v>
+        <v>105.01</v>
       </c>
       <c r="D9" t="n">
-        <v>8.01</v>
+        <v>8.1</v>
       </c>
       <c r="E9" t="n">
-        <v>112.41</v>
+        <v>112.8</v>
       </c>
       <c r="F9" t="n">
-        <v>115.98</v>
+        <v>116.54</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1303.7</v>
+        <v>1303.3</v>
       </c>
       <c r="C10" t="n">
-        <v>958.3200000000001</v>
+        <v>958.3</v>
       </c>
       <c r="D10" t="n">
         <v>53.63</v>
       </c>
       <c r="E10" t="n">
-        <v>1142.82</v>
+        <v>1142.42</v>
       </c>
       <c r="F10" t="n">
-        <v>1108.14</v>
+        <v>1107.81</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>231.1</v>
+        <v>230.41</v>
       </c>
       <c r="C11" t="n">
-        <v>209.3</v>
+        <v>209.27</v>
       </c>
       <c r="D11" t="n">
-        <v>8.970000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="E11" t="n">
-        <v>204.19</v>
+        <v>203.43</v>
       </c>
       <c r="F11" t="n">
-        <v>196.44</v>
+        <v>195.85</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,19 +3403,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.95</v>
+        <v>20.7</v>
       </c>
       <c r="C12" t="n">
-        <v>17.49</v>
+        <v>17.48</v>
       </c>
       <c r="D12" t="n">
         <v>1.1</v>
       </c>
       <c r="E12" t="n">
-        <v>17.65</v>
+        <v>17.39</v>
       </c>
       <c r="F12" t="n">
-        <v>17.81</v>
+        <v>17.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>526.8</v>
+        <v>525.25</v>
       </c>
       <c r="C13" t="n">
-        <v>463.12</v>
+        <v>463.05</v>
       </c>
       <c r="D13" t="n">
         <v>24.97</v>
       </c>
       <c r="E13" t="n">
-        <v>451.9</v>
+        <v>450.35</v>
       </c>
       <c r="F13" t="n">
-        <v>447.78</v>
+        <v>446.46</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264.15</v>
+        <v>266.3</v>
       </c>
       <c r="C15" t="n">
-        <v>237.4</v>
+        <v>237.48</v>
       </c>
       <c r="D15" t="n">
         <v>15.97</v>
       </c>
       <c r="E15" t="n">
-        <v>216.23</v>
+        <v>218.38</v>
       </c>
       <c r="F15" t="n">
-        <v>224.53</v>
+        <v>226.35</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 08:12</t>
+          <t>Generated: 2026-06-04 08:49</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127832209736098</v>
+        <v>0.1128131974554543</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0844118651575632</v>
+        <v>0.0844301449822687</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746550375991023</v>
+        <v>0.0746748800487137</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.121255661517973</v>
+        <v>0.1212865599489856</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0952934346546469</v>
+        <v>0.0953187625526193</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06894726286613161</v>
+        <v>0.0689661340582496</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0959678292115399</v>
+        <v>0.09561298518243309</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06826258741533579</v>
+        <v>0.0682766365425414</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09360827560054941</v>
+        <v>0.0937440149756511</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08309255094566879</v>
+        <v>0.08312393729966749</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506661307155445</v>
+        <v>0.0506795971898517</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510561433423345</v>
+        <v>0.0510731497635634</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08307633602336</v>
+        <v>0.09360827560054941</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08309255094566879</v>
+        <v>0.0937440149756511</v>
       </c>
       <c r="D4" t="n">
-        <v>1.621492230879928e-05</v>
+        <v>0.0001357393751016</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0844007811999028</v>
+        <v>0.08309255094566879</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0844118651575632</v>
+        <v>0.08312393729966749</v>
       </c>
       <c r="D5" t="n">
-        <v>1.108395766040438e-05</v>
+        <v>3.138635399869971e-05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1212451642333992</v>
+        <v>0.121255661517973</v>
       </c>
       <c r="C6" t="n">
-        <v>0.121255661517973</v>
+        <v>0.1212865599489856</v>
       </c>
       <c r="D6" t="n">
-        <v>1.049728457379329e-05</v>
+        <v>3.089843101260203e-05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09596048915885461</v>
+        <v>0.1127832209736098</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0959678292115399</v>
+        <v>0.1128131974554543</v>
       </c>
       <c r="D7" t="n">
-        <v>7.34005268529514e-06</v>
+        <v>2.997648184450974e-05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1127788171159506</v>
+        <v>0.0952934346546469</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1127832209736098</v>
+        <v>0.0953187625526193</v>
       </c>
       <c r="D8" t="n">
-        <v>4.403857659193711e-06</v>
+        <v>2.532789797239643e-05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0952897137224155</v>
+        <v>0.0746550375991023</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0952934346546469</v>
+        <v>0.0746748800487137</v>
       </c>
       <c r="D9" t="n">
-        <v>3.720932231401908e-06</v>
+        <v>1.984244961139581e-05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0746521225364157</v>
+        <v>0.06894726286613161</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0746550375991023</v>
+        <v>0.0689661340582496</v>
       </c>
       <c r="D10" t="n">
-        <v>2.915062686598135e-06</v>
+        <v>1.887119211799182e-05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0506641523500936</v>
+        <v>0.0844118651575632</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0506661307155445</v>
+        <v>0.0844301449822687</v>
       </c>
       <c r="D11" t="n">
-        <v>1.978365450905351e-06</v>
+        <v>1.827982470549439e-05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0682639501572225</v>
+        <v>0.0510561433423345</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06826258741533579</v>
+        <v>0.0510731497635634</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.362741886709595e-06</v>
+        <v>1.700642122889895e-05</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0510603069736102</v>
+        <v>0.06826258741533579</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0510561433423345</v>
+        <v>0.0682766365425414</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.163631275699853e-06</v>
+        <v>1.404912720560925e-05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09362979868343391</v>
+        <v>0.0506661307155445</v>
       </c>
       <c r="C14" t="n">
-        <v>0.09360827560054941</v>
+        <v>0.0506795971898517</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.152308288450033e-05</v>
+        <v>1.346647430719439e-05</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0689783678453408</v>
+        <v>0.0959678292115399</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06894726286613161</v>
+        <v>0.09561298518243309</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.110497920918998e-05</v>
+        <v>-0.0003548440291068</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3179,19 +3179,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200.96</v>
+        <v>201.6</v>
       </c>
       <c r="C5" t="n">
-        <v>132.3</v>
+        <v>132.32</v>
       </c>
       <c r="D5" t="n">
         <v>10.35</v>
       </c>
       <c r="E5" t="n">
-        <v>169.9</v>
+        <v>170.54</v>
       </c>
       <c r="F5" t="n">
-        <v>170.82</v>
+        <v>171.36</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10135.5</v>
+        <v>10142.5</v>
       </c>
       <c r="C7" t="n">
-        <v>8887.299999999999</v>
+        <v>8887.58</v>
       </c>
       <c r="D7" t="n">
         <v>337.75</v>
       </c>
       <c r="E7" t="n">
-        <v>9122.25</v>
+        <v>9129.25</v>
       </c>
       <c r="F7" t="n">
-        <v>8615.17</v>
+        <v>8621.120000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1303.3</v>
+        <v>1324.1</v>
       </c>
       <c r="C10" t="n">
-        <v>958.3</v>
+        <v>959.12</v>
       </c>
       <c r="D10" t="n">
-        <v>53.63</v>
+        <v>54.23</v>
       </c>
       <c r="E10" t="n">
-        <v>1142.42</v>
+        <v>1161.42</v>
       </c>
       <c r="F10" t="n">
-        <v>1107.81</v>
+        <v>1125.48</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>230.41</v>
+        <v>230.05</v>
       </c>
       <c r="C11" t="n">
-        <v>209.27</v>
+        <v>209.26</v>
       </c>
       <c r="D11" t="n">
         <v>8.99</v>
       </c>
       <c r="E11" t="n">
-        <v>203.43</v>
+        <v>203.07</v>
       </c>
       <c r="F11" t="n">
-        <v>195.85</v>
+        <v>195.54</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.7</v>
+        <v>20.75</v>
       </c>
       <c r="C12" t="n">
         <v>17.48</v>
@@ -3412,10 +3412,10 @@
         <v>1.1</v>
       </c>
       <c r="E12" t="n">
-        <v>17.39</v>
+        <v>17.44</v>
       </c>
       <c r="F12" t="n">
-        <v>17.6</v>
+        <v>17.64</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>525.25</v>
+        <v>524</v>
       </c>
       <c r="C13" t="n">
-        <v>463.05</v>
+        <v>463.01</v>
       </c>
       <c r="D13" t="n">
         <v>24.97</v>
       </c>
       <c r="E13" t="n">
-        <v>450.35</v>
+        <v>449.1</v>
       </c>
       <c r="F13" t="n">
-        <v>446.46</v>
+        <v>445.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>266.3</v>
+        <v>265.5</v>
       </c>
       <c r="C15" t="n">
-        <v>237.48</v>
+        <v>237.45</v>
       </c>
       <c r="D15" t="n">
         <v>15.97</v>
       </c>
       <c r="E15" t="n">
-        <v>218.38</v>
+        <v>217.58</v>
       </c>
       <c r="F15" t="n">
-        <v>226.35</v>
+        <v>225.68</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 08:49</t>
+          <t>Generated: 2026-06-04 10:33</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1128131974554543</v>
+        <v>0.1127410033006557</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0844301449822687</v>
+        <v>0.0843651708398247</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746748800487137</v>
+        <v>0.074627092290088</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1212865599489856</v>
+        <v>0.1212337164742957</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0953187625526193</v>
+        <v>0.09525776386049691</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689661340582496</v>
+        <v>0.0689690552237766</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09561298518243309</v>
+        <v>0.0960143018785725</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682766365425414</v>
+        <v>0.0682327559947148</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0937440149756511</v>
+        <v>0.09380746758023489</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08312393729966749</v>
+        <v>0.08306144670637119</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506795971898517</v>
+        <v>0.0506471650740428</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510731497635634</v>
+        <v>0.0510430607769256</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09360827560054941</v>
+        <v>0.09561298518243309</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0937440149756511</v>
+        <v>0.0960143018785725</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001357393751016</v>
+        <v>0.0004013166961394</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08309255094566879</v>
+        <v>0.0937440149756511</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08312393729966749</v>
+        <v>0.09380746758023489</v>
       </c>
       <c r="D5" t="n">
-        <v>3.138635399869971e-05</v>
+        <v>6.345260458379132e-05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.121255661517973</v>
+        <v>0.0689661340582496</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1212865599489856</v>
+        <v>0.0689690552237766</v>
       </c>
       <c r="D6" t="n">
-        <v>3.089843101260203e-05</v>
+        <v>2.921165526997838e-06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1127832209736098</v>
+        <v>0.0510731497635634</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1128131974554543</v>
+        <v>0.0510430607769256</v>
       </c>
       <c r="D7" t="n">
-        <v>2.997648184450974e-05</v>
+        <v>-3.00889866377968e-05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0952934346546469</v>
+        <v>0.0506795971898517</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0953187625526193</v>
+        <v>0.0506471650740428</v>
       </c>
       <c r="D8" t="n">
-        <v>2.532789797239643e-05</v>
+        <v>-3.24321158088961e-05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0746550375991023</v>
+        <v>0.0682766365425414</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0746748800487137</v>
+        <v>0.0682327559947148</v>
       </c>
       <c r="D9" t="n">
-        <v>1.984244961139581e-05</v>
+        <v>-4.388054782659967e-05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06894726286613161</v>
+        <v>0.0746748800487137</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0689661340582496</v>
+        <v>0.074627092290088</v>
       </c>
       <c r="D10" t="n">
-        <v>1.887119211799182e-05</v>
+        <v>-4.778775862569751e-05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0844118651575632</v>
+        <v>0.1212865599489856</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0844301449822687</v>
+        <v>0.1212337164742957</v>
       </c>
       <c r="D11" t="n">
-        <v>1.827982470549439e-05</v>
+        <v>-5.284347468989536e-05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0510561433423345</v>
+        <v>0.0953187625526193</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0510731497635634</v>
+        <v>0.09525776386049691</v>
       </c>
       <c r="D12" t="n">
-        <v>1.700642122889895e-05</v>
+        <v>-6.099869212239373e-05</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06826258741533579</v>
+        <v>0.08312393729966749</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0682766365425414</v>
+        <v>0.08306144670637119</v>
       </c>
       <c r="D13" t="n">
-        <v>1.404912720560925e-05</v>
+        <v>-6.249059329629936e-05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506661307155445</v>
+        <v>0.0844301449822687</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0506795971898517</v>
+        <v>0.0843651708398247</v>
       </c>
       <c r="D14" t="n">
-        <v>1.346647430719439e-05</v>
+        <v>-6.497414244399646e-05</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0959678292115399</v>
+        <v>0.1128131974554543</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09561298518243309</v>
+        <v>0.1127410033006557</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0003548440291068</v>
+        <v>-7.219415479860214e-05</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3179,19 +3179,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>201.6</v>
+        <v>197.08</v>
       </c>
       <c r="C5" t="n">
-        <v>132.32</v>
+        <v>132.15</v>
       </c>
       <c r="D5" t="n">
         <v>10.35</v>
       </c>
       <c r="E5" t="n">
-        <v>170.54</v>
+        <v>166.02</v>
       </c>
       <c r="F5" t="n">
-        <v>171.36</v>
+        <v>167.52</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10142.5</v>
+        <v>10098</v>
       </c>
       <c r="C7" t="n">
-        <v>8887.58</v>
+        <v>8885.83</v>
       </c>
       <c r="D7" t="n">
         <v>337.75</v>
       </c>
       <c r="E7" t="n">
-        <v>9129.25</v>
+        <v>9084.75</v>
       </c>
       <c r="F7" t="n">
-        <v>8621.120000000001</v>
+        <v>8583.299999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3307,19 +3307,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137.1</v>
+        <v>136.16</v>
       </c>
       <c r="C9" t="n">
-        <v>105.01</v>
+        <v>104.97</v>
       </c>
       <c r="D9" t="n">
         <v>8.1</v>
       </c>
       <c r="E9" t="n">
-        <v>112.8</v>
+        <v>111.86</v>
       </c>
       <c r="F9" t="n">
-        <v>116.54</v>
+        <v>115.74</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1324.1</v>
+        <v>1295</v>
       </c>
       <c r="C10" t="n">
-        <v>959.12</v>
+        <v>957.98</v>
       </c>
       <c r="D10" t="n">
         <v>54.23</v>
       </c>
       <c r="E10" t="n">
-        <v>1161.42</v>
+        <v>1132.32</v>
       </c>
       <c r="F10" t="n">
-        <v>1125.48</v>
+        <v>1100.75</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>230.05</v>
+        <v>230.03</v>
       </c>
       <c r="C11" t="n">
         <v>209.26</v>
       </c>
       <c r="D11" t="n">
-        <v>8.99</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>203.07</v>
+        <v>202.92</v>
       </c>
       <c r="F11" t="n">
-        <v>195.54</v>
+        <v>195.53</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,19 +3403,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.75</v>
+        <v>20.9</v>
       </c>
       <c r="C12" t="n">
-        <v>17.48</v>
+        <v>17.54</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="E12" t="n">
-        <v>17.44</v>
+        <v>17.8</v>
       </c>
       <c r="F12" t="n">
-        <v>17.64</v>
+        <v>17.76</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>524</v>
+        <v>525.25</v>
       </c>
       <c r="C13" t="n">
-        <v>463.01</v>
+        <v>463.05</v>
       </c>
       <c r="D13" t="n">
         <v>24.97</v>
       </c>
       <c r="E13" t="n">
-        <v>449.1</v>
+        <v>450.35</v>
       </c>
       <c r="F13" t="n">
-        <v>445.4</v>
+        <v>446.46</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>265.5</v>
+        <v>264.25</v>
       </c>
       <c r="C15" t="n">
-        <v>237.45</v>
+        <v>237.4</v>
       </c>
       <c r="D15" t="n">
-        <v>15.97</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>217.58</v>
+        <v>216.26</v>
       </c>
       <c r="F15" t="n">
-        <v>225.68</v>
+        <v>224.61</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 10:33</t>
+          <t>Generated: 2026-06-04 10:55</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Current Regime: BEAR</t>
+          <t>Current Regime: STRONG_BEAR</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127410033006557</v>
+        <v>0.1127410040880248</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0843651708398247</v>
+        <v>0.0843651659109189</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.074627092290088</v>
+        <v>0.0746270928112743</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1212337164742957</v>
+        <v>0.1212337158552034</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09525776386049691</v>
+        <v>0.0952577645257652</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689690552237766</v>
+        <v>0.0689690557054478</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0960143018785725</v>
+        <v>0.09601430254912439</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682327559947148</v>
+        <v>0.0682327564712439</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09380746758023489</v>
+        <v>0.0938074682353745</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08306144670637119</v>
+        <v>0.083061447286462</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506471650740428</v>
+        <v>0.0506471654277562</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510430607769256</v>
+        <v>0.0510430611334039</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09561298518243309</v>
+        <v>0.1127410033006557</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0960143018785725</v>
+        <v>0.1127410040880248</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004013166961394</v>
+        <v>7.873691004744997e-10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0937440149756511</v>
+        <v>0.0960143018785725</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09380746758023489</v>
+        <v>0.09601430254912439</v>
       </c>
       <c r="D5" t="n">
-        <v>6.345260458379132e-05</v>
+        <v>6.705518917904384e-10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0689661340582496</v>
+        <v>0.09525776386049691</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0689690552237766</v>
+        <v>0.0952577645257652</v>
       </c>
       <c r="D6" t="n">
-        <v>2.921165526997838e-06</v>
+        <v>6.65268298782884e-10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0510731497635634</v>
+        <v>0.09380746758023489</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0510430607769256</v>
+        <v>0.0938074682353745</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.00889866377968e-05</v>
+        <v>6.551396092291384e-10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0506795971898517</v>
+        <v>0.08306144670637119</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0506471650740428</v>
+        <v>0.083061447286462</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.24321158088961e-05</v>
+        <v>5.800908087216783e-10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0682766365425414</v>
+        <v>0.074627092290088</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0682327559947148</v>
+        <v>0.0746270928112743</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.388054782659967e-05</v>
+        <v>5.211863024490171e-10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0746748800487137</v>
+        <v>0.0689690552237766</v>
       </c>
       <c r="C10" t="n">
-        <v>0.074627092290088</v>
+        <v>0.0689690557054478</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.778775862569751e-05</v>
+        <v>4.816712029231951e-10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1212865599489856</v>
+        <v>0.0682327559947148</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1212337164742957</v>
+        <v>0.0682327564712439</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.284347468989536e-05</v>
+        <v>4.765290939623411e-10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0953187625526193</v>
+        <v>0.0510430607769256</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09525776386049691</v>
+        <v>0.0510430611334039</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.099869212239373e-05</v>
+        <v>3.56478298269014e-10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08312393729966749</v>
+        <v>0.0506471650740428</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08306144670637119</v>
+        <v>0.0506471654277562</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.249059329629936e-05</v>
+        <v>3.537133988484875e-10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0844301449822687</v>
+        <v>0.1212337164742957</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0843651708398247</v>
+        <v>0.1212337158552034</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.497414244399646e-05</v>
+        <v>-6.190923051985209e-10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1128131974554543</v>
+        <v>0.0843651708398247</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1127410033006557</v>
+        <v>0.0843651659109189</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.219415479860214e-05</v>
+        <v>-4.928905797396688e-09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3163,12 +3163,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3259,12 +3259,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3291,12 +3291,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3387,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3451,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>REGIME</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 10:55</t>
+          <t>Generated: 2026-06-04 12:39</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Current Regime: STRONG_BEAR</t>
+          <t>Current Regime: UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127410040880248</v>
+        <v>0.1127441479887827</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0843651659109189</v>
+        <v>0.0843675185217653</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746270928112743</v>
+        <v>0.0746291738657721</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1212337158552034</v>
+        <v>0.1212370893589929</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0952577645257652</v>
+        <v>0.095260420888111</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689690557054478</v>
+        <v>0.06897097464294071</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09601430254912439</v>
+        <v>0.0959891055247684</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682327564712439</v>
+        <v>0.0682346592129883</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0938074682353745</v>
+        <v>0.09381008415469209</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.083061447286462</v>
+        <v>0.0830637635417516</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506471654277562</v>
+        <v>0.0506485777769105</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510430611334039</v>
+        <v>0.0510444845225238</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127410033006557</v>
+        <v>0.1212337158552034</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1127410040880248</v>
+        <v>0.1212370893589929</v>
       </c>
       <c r="D4" t="n">
-        <v>7.873691004744997e-10</v>
+        <v>3.37350378949719e-06</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0960143018785725</v>
+        <v>0.1127410040880248</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09601430254912439</v>
+        <v>0.1127441479887827</v>
       </c>
       <c r="D5" t="n">
-        <v>6.705518917904384e-10</v>
+        <v>3.143900757895945e-06</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09525776386049691</v>
+        <v>0.0952577645257652</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0952577645257652</v>
+        <v>0.095260420888111</v>
       </c>
       <c r="D6" t="n">
-        <v>6.65268298782884e-10</v>
+        <v>2.656362345795915e-06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09380746758023489</v>
+        <v>0.0938074682353745</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0938074682353745</v>
+        <v>0.09381008415469209</v>
       </c>
       <c r="D7" t="n">
-        <v>6.551396092291384e-10</v>
+        <v>2.615919317591753e-06</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08306144670637119</v>
+        <v>0.0843651659109189</v>
       </c>
       <c r="C8" t="n">
-        <v>0.083061447286462</v>
+        <v>0.0843675185217653</v>
       </c>
       <c r="D8" t="n">
-        <v>5.800908087216783e-10</v>
+        <v>2.352610846398373e-06</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.074627092290088</v>
+        <v>0.083061447286462</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0746270928112743</v>
+        <v>0.0830637635417516</v>
       </c>
       <c r="D9" t="n">
-        <v>5.211863024490171e-10</v>
+        <v>2.316255289597224e-06</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0689690552237766</v>
+        <v>0.0746270928112743</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0689690557054478</v>
+        <v>0.0746291738657721</v>
       </c>
       <c r="D10" t="n">
-        <v>4.816712029231951e-10</v>
+        <v>2.081054497796164e-06</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682327559947148</v>
+        <v>0.0689690557054478</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0682327564712439</v>
+        <v>0.06897097464294071</v>
       </c>
       <c r="D11" t="n">
-        <v>4.765290939623411e-10</v>
+        <v>1.918937492906281e-06</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0510430607769256</v>
+        <v>0.0682327564712439</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0510430611334039</v>
+        <v>0.0682346592129883</v>
       </c>
       <c r="D12" t="n">
-        <v>3.56478298269014e-10</v>
+        <v>1.902741744400083e-06</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0506471650740428</v>
+        <v>0.0510430611334039</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0506471654277562</v>
+        <v>0.0510444845225238</v>
       </c>
       <c r="D13" t="n">
-        <v>3.537133988484875e-10</v>
+        <v>1.423389119903362e-06</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1212337164742957</v>
+        <v>0.0506471654277562</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1212337158552034</v>
+        <v>0.0506485777769105</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.190923051985209e-10</v>
+        <v>1.41234915430194e-06</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0843651708398247</v>
+        <v>0.09601430254912439</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0843651659109189</v>
+        <v>0.0959891055247684</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.928905797396688e-09</v>
+        <v>-2.519702435599402e-05</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1295</v>
+        <v>1298.2</v>
       </c>
       <c r="C10" t="n">
-        <v>957.98</v>
+        <v>958.1</v>
       </c>
       <c r="D10" t="n">
         <v>54.23</v>
       </c>
       <c r="E10" t="n">
-        <v>1132.32</v>
+        <v>1135.52</v>
       </c>
       <c r="F10" t="n">
-        <v>1100.75</v>
+        <v>1103.47</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 12:39</t>
+          <t>Generated: 2026-06-04 13:08</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127441479887827</v>
+        <v>0.1127441463867804</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0843675185217653</v>
+        <v>0.0843675228412271</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746291738657721</v>
+        <v>0.0746291728053525</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1212370893589929</v>
+        <v>0.1212370963272412</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.095260420888111</v>
+        <v>0.0952604195345382</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06897097464294071</v>
+        <v>0.0689709736629194</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0959891055247684</v>
+        <v>0.0959891041608416</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682346592129883</v>
+        <v>0.0682346582434295</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09381008415469209</v>
+        <v>0.0938100828217274</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0830637635417516</v>
+        <v>0.0830637623614833</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506485777769105</v>
+        <v>0.0506485770572355</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510444845225238</v>
+        <v>0.0510444837972233</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1212337158552034</v>
+        <v>0.1212370893589929</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1212370893589929</v>
+        <v>0.1212370963272412</v>
       </c>
       <c r="D4" t="n">
-        <v>3.37350378949719e-06</v>
+        <v>6.968248297822832e-09</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1127410040880248</v>
+        <v>0.0843675185217653</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1127441479887827</v>
+        <v>0.0843675228412271</v>
       </c>
       <c r="D5" t="n">
-        <v>3.143900757895945e-06</v>
+        <v>4.319461802126945e-09</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0952577645257652</v>
+        <v>0.0506485777769105</v>
       </c>
       <c r="C6" t="n">
-        <v>0.095260420888111</v>
+        <v>0.0506485770572355</v>
       </c>
       <c r="D6" t="n">
-        <v>2.656362345795915e-06</v>
+        <v>-7.196750001492447e-10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0938074682353745</v>
+        <v>0.0510444845225238</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09381008415469209</v>
+        <v>0.0510444837972233</v>
       </c>
       <c r="D7" t="n">
-        <v>2.615919317591753e-06</v>
+        <v>-7.253005002150202e-10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0843651659109189</v>
+        <v>0.0682346592129883</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0843675185217653</v>
+        <v>0.0682346582434295</v>
       </c>
       <c r="D8" t="n">
-        <v>2.352610846398373e-06</v>
+        <v>-9.69558794361447e-10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.083061447286462</v>
+        <v>0.06897097464294071</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0830637635417516</v>
+        <v>0.0689709736629194</v>
       </c>
       <c r="D9" t="n">
-        <v>2.316255289597224e-06</v>
+        <v>-9.800213002231215e-10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0746270928112743</v>
+        <v>0.0746291738657721</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0746291738657721</v>
+        <v>0.0746291728053525</v>
       </c>
       <c r="D10" t="n">
-        <v>2.081054497796164e-06</v>
+        <v>-1.060419599352435e-09</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0689690557054478</v>
+        <v>0.0830637635417516</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06897097464294071</v>
+        <v>0.0830637623614833</v>
       </c>
       <c r="D11" t="n">
-        <v>1.918937492906281e-06</v>
+        <v>-1.180268299760811e-09</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0682327564712439</v>
+        <v>0.09381008415469209</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0682346592129883</v>
+        <v>0.0938100828217274</v>
       </c>
       <c r="D12" t="n">
-        <v>1.902741744400083e-06</v>
+        <v>-1.332964696953987e-09</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0510430611334039</v>
+        <v>0.095260420888111</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0510444845225238</v>
+        <v>0.0952604195345382</v>
       </c>
       <c r="D13" t="n">
-        <v>1.423389119903362e-06</v>
+        <v>-1.353572795514957e-09</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506471654277562</v>
+        <v>0.0959891055247684</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0506485777769105</v>
+        <v>0.0959891041608416</v>
       </c>
       <c r="D14" t="n">
-        <v>1.41234915430194e-06</v>
+        <v>-1.36392680483155e-09</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09601430254912439</v>
+        <v>0.1127441479887827</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0959891055247684</v>
+        <v>0.1127441463867804</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.519702435599402e-05</v>
+        <v>-1.602002294709415e-09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 13:08</t>
+          <t>Generated: 2026-06-04 18:06</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127441463867804</v>
+        <v>0.1127441452022032</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0843675228412271</v>
+        <v>0.0843675219547967</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746291728053525</v>
+        <v>0.0746291720212407</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1212370963272412</v>
+        <v>0.1212371006723774</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0952604195345382</v>
+        <v>0.0952604185336586</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689709736629194</v>
+        <v>0.0689709772749824</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0959891041608416</v>
+        <v>0.0959891031523059</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682346582434295</v>
+        <v>0.0682346575265034</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0938100828217274</v>
+        <v>0.0938100818360862</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0830637623614833</v>
+        <v>0.0830637620398518</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506485770572355</v>
+        <v>0.0506485765250824</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510444837972233</v>
+        <v>0.0510444832609105</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1212370893589929</v>
+        <v>0.1212370963272412</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1212370963272412</v>
+        <v>0.1212371006723774</v>
       </c>
       <c r="D4" t="n">
-        <v>6.968248297822832e-09</v>
+        <v>4.345136209171763e-09</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0843675185217653</v>
+        <v>0.0689709736629194</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0843675228412271</v>
+        <v>0.0689709772749824</v>
       </c>
       <c r="D5" t="n">
-        <v>4.319461802126945e-09</v>
+        <v>3.612062995927978e-09</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0506485777769105</v>
+        <v>0.0830637623614833</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0506485770572355</v>
+        <v>0.0830637620398518</v>
       </c>
       <c r="D6" t="n">
-        <v>-7.196750001492447e-10</v>
+        <v>-3.216314992116054e-10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0510444845225238</v>
+        <v>0.0506485770572355</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0510444837972233</v>
+        <v>0.0506485765250824</v>
       </c>
       <c r="D7" t="n">
-        <v>-7.253005002150202e-10</v>
+        <v>-5.321530993640522e-10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0682346592129883</v>
+        <v>0.0510444837972233</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0682346582434295</v>
+        <v>0.0510444832609105</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.69558794361447e-10</v>
+        <v>-5.363127997259909e-10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06897097464294071</v>
+        <v>0.0682346582434295</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0689709736629194</v>
+        <v>0.0682346575265034</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.800213002231215e-10</v>
+        <v>-7.169261018180605e-10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0746291738657721</v>
+        <v>0.0746291728053525</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0746291728053525</v>
+        <v>0.0746291720212407</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.060419599352435e-09</v>
+        <v>-7.841118032647643e-10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0830637635417516</v>
+        <v>0.0843675228412271</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0830637623614833</v>
+        <v>0.0843675219547967</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.180268299760811e-09</v>
+        <v>-8.864304013034284e-10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09381008415469209</v>
+        <v>0.0938100828217274</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0938100828217274</v>
+        <v>0.0938100818360862</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.332964696953987e-09</v>
+        <v>-9.85641193662623e-10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3010,13 +3010,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.095260420888111</v>
+        <v>0.0952604195345382</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0952604195345382</v>
+        <v>0.0952604185336586</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.353572795514957e-09</v>
+        <v>-1.000879601420479e-09</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0959891055247684</v>
+        <v>0.0959891041608416</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0959891041608416</v>
+        <v>0.0959891031523059</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.36392680483155e-09</v>
+        <v>-1.008535699398294e-09</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1127441479887827</v>
+        <v>0.1127441463867804</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1127441463867804</v>
+        <v>0.1127441452022032</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.602002294709415e-09</v>
+        <v>-1.184577200219472e-09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 18:06</t>
+          <t>Generated: 2026-06-04 22:56</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1127441452022032</v>
+        <v>0.1128236273353456</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0843675219547967</v>
+        <v>0.0843133943098679</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746291720212407</v>
+        <v>0.0746993770181873</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1212371006723774</v>
+        <v>0.1211537154453593</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0952604185336586</v>
+        <v>0.0953878286689681</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689709772749824</v>
+        <v>0.0690269632251086</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0959891031523059</v>
+        <v>0.0957788888064333</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682346575265034</v>
+        <v>0.0681895381427637</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0938100818360862</v>
+        <v>0.09390296627179059</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0830637620398518</v>
+        <v>0.0830391754619135</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0506485765250824</v>
+        <v>0.050682899130712</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510444832609105</v>
+        <v>0.0510016261835496</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1212370963272412</v>
+        <v>0.0952604185336586</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1212371006723774</v>
+        <v>0.0953878286689681</v>
       </c>
       <c r="D4" t="n">
-        <v>4.345136209171763e-09</v>
+        <v>0.0001274101353094</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0689709736629194</v>
+        <v>0.0938100818360862</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0689709772749824</v>
+        <v>0.09390296627179059</v>
       </c>
       <c r="D5" t="n">
-        <v>3.612062995927978e-09</v>
+        <v>9.288443570439064e-05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0830637623614833</v>
+        <v>0.1127441452022032</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0830637620398518</v>
+        <v>0.1128236273353456</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.216314992116054e-10</v>
+        <v>7.948213314239172e-05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0506485770572355</v>
+        <v>0.0746291720212407</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0506485765250824</v>
+        <v>0.0746993770181873</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.321530993640522e-10</v>
+        <v>7.020499694659899e-05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0510444837972233</v>
+        <v>0.0689709772749824</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0510444832609105</v>
+        <v>0.0690269632251086</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.363127997259909e-10</v>
+        <v>5.598595012619445e-05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0682346582434295</v>
+        <v>0.0506485765250824</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0682346575265034</v>
+        <v>0.050682899130712</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.169261018180605e-10</v>
+        <v>3.432260562959838e-05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0746291728053525</v>
+        <v>0.0830637620398518</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0746291720212407</v>
+        <v>0.0830391754619135</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.841118032647643e-10</v>
+        <v>-2.458657793830143e-05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0843675228412271</v>
+        <v>0.0510444832609105</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0843675219547967</v>
+        <v>0.0510016261835496</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.864304013034284e-10</v>
+        <v>-4.285707736090272e-05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0938100828217274</v>
+        <v>0.0682346575265034</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0938100818360862</v>
+        <v>0.0681895381427637</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.85641193662623e-10</v>
+        <v>-4.511938373970292e-05</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0952604195345382</v>
+        <v>0.0843675219547967</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0952604185336586</v>
+        <v>0.0843133943098679</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.000879601420479e-09</v>
+        <v>-5.412764492880584e-05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0959891041608416</v>
+        <v>0.1212371006723774</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0959891031523059</v>
+        <v>0.1211537154453593</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.008535699398294e-09</v>
+        <v>-8.338522701810402e-05</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1127441463867804</v>
+        <v>0.0959891031523059</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1127441452022032</v>
+        <v>0.0957788888064333</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.184577200219472e-09</v>
+        <v>-0.0002102143458725</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3147,19 +3147,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>651.6</v>
+        <v>620.6</v>
       </c>
       <c r="C4" t="n">
-        <v>374.23</v>
+        <v>362.91</v>
       </c>
       <c r="D4" t="n">
-        <v>25.32</v>
+        <v>24.62</v>
       </c>
       <c r="E4" t="n">
-        <v>575.64</v>
+        <v>546.73</v>
       </c>
       <c r="F4" t="n">
-        <v>553.86</v>
+        <v>527.51</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3179,19 +3179,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>197.08</v>
+        <v>199.41</v>
       </c>
       <c r="C5" t="n">
-        <v>132.15</v>
+        <v>129.5</v>
       </c>
       <c r="D5" t="n">
-        <v>10.35</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>166.02</v>
+        <v>169.53</v>
       </c>
       <c r="F5" t="n">
-        <v>167.52</v>
+        <v>169.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>458.7</v>
+        <v>436.9</v>
       </c>
       <c r="C6" t="n">
-        <v>299.71</v>
+        <v>293.22</v>
       </c>
       <c r="D6" t="n">
-        <v>21.04</v>
+        <v>20.77</v>
       </c>
       <c r="E6" t="n">
-        <v>395.6</v>
+        <v>374.59</v>
       </c>
       <c r="F6" t="n">
-        <v>389.9</v>
+        <v>371.36</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10098</v>
+        <v>9997.5</v>
       </c>
       <c r="C7" t="n">
-        <v>8885.83</v>
+        <v>8836.360000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>337.75</v>
+        <v>322.92</v>
       </c>
       <c r="E7" t="n">
-        <v>9084.75</v>
+        <v>9028.719999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>8583.299999999999</v>
+        <v>8497.879999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3275,19 +3275,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1555.8</v>
+        <v>1481.8</v>
       </c>
       <c r="C8" t="n">
-        <v>1050.69</v>
+        <v>1030.07</v>
       </c>
       <c r="D8" t="n">
-        <v>55.75</v>
+        <v>54.65</v>
       </c>
       <c r="E8" t="n">
-        <v>1388.56</v>
+        <v>1317.84</v>
       </c>
       <c r="F8" t="n">
-        <v>1322.43</v>
+        <v>1259.53</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3307,19 +3307,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136.16</v>
+        <v>130.97</v>
       </c>
       <c r="C9" t="n">
-        <v>104.97</v>
+        <v>103.7</v>
       </c>
       <c r="D9" t="n">
-        <v>8.1</v>
+        <v>7.79</v>
       </c>
       <c r="E9" t="n">
-        <v>111.86</v>
+        <v>107.59</v>
       </c>
       <c r="F9" t="n">
-        <v>115.74</v>
+        <v>111.32</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1298.2</v>
+        <v>1272</v>
       </c>
       <c r="C10" t="n">
-        <v>958.1</v>
+        <v>944.22</v>
       </c>
       <c r="D10" t="n">
-        <v>54.23</v>
+        <v>54.13</v>
       </c>
       <c r="E10" t="n">
-        <v>1135.52</v>
+        <v>1109.62</v>
       </c>
       <c r="F10" t="n">
-        <v>1103.47</v>
+        <v>1081.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>230.03</v>
+        <v>232.52</v>
       </c>
       <c r="C11" t="n">
-        <v>209.26</v>
+        <v>208.41</v>
       </c>
       <c r="D11" t="n">
-        <v>9.039999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="E11" t="n">
-        <v>202.92</v>
+        <v>205.73</v>
       </c>
       <c r="F11" t="n">
-        <v>195.53</v>
+        <v>197.64</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,19 +3403,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.9</v>
+        <v>20.1</v>
       </c>
       <c r="C12" t="n">
-        <v>17.54</v>
+        <v>17.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="E12" t="n">
-        <v>17.8</v>
+        <v>17.03</v>
       </c>
       <c r="F12" t="n">
-        <v>17.76</v>
+        <v>17.09</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>525.25</v>
+        <v>512.5</v>
       </c>
       <c r="C13" t="n">
-        <v>463.05</v>
+        <v>460.52</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97</v>
+        <v>24.26</v>
       </c>
       <c r="E13" t="n">
-        <v>450.35</v>
+        <v>439.71</v>
       </c>
       <c r="F13" t="n">
-        <v>446.46</v>
+        <v>435.62</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3467,19 +3467,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>915.35</v>
+        <v>871.8</v>
       </c>
       <c r="C14" t="n">
-        <v>698.9299999999999</v>
+        <v>690.1</v>
       </c>
       <c r="D14" t="n">
-        <v>40.08</v>
+        <v>39.4</v>
       </c>
       <c r="E14" t="n">
-        <v>795.1</v>
+        <v>753.61</v>
       </c>
       <c r="F14" t="n">
-        <v>778.05</v>
+        <v>741.03</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264.25</v>
+        <v>262.5</v>
       </c>
       <c r="C15" t="n">
-        <v>237.4</v>
+        <v>236.31</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.82</v>
       </c>
       <c r="E15" t="n">
-        <v>216.26</v>
+        <v>215.04</v>
       </c>
       <c r="F15" t="n">
-        <v>224.61</v>
+        <v>223.12</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 22:56</t>
+          <t>Generated: 2026-06-05 08:08</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1128236273353456</v>
+        <v>0.1123654397155705</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0843133943098679</v>
+        <v>0.0845074779896217</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0746993770181873</v>
+        <v>0.074301914547207</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1211537154453593</v>
+        <v>0.1218573242802931</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0953878286689681</v>
+        <v>0.0948654266546021</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0690269632251086</v>
+        <v>0.0689195103012013</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0957788888064333</v>
+        <v>0.0961057170822027</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0681895381427637</v>
+        <v>0.0680987670583674</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09390296627179059</v>
+        <v>0.0936182971626163</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0830391754619135</v>
+        <v>0.08304059726984241</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.050682899130712</v>
+        <v>0.0513831263429593</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510016261835496</v>
+        <v>0.0509364015955158</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0952604185336586</v>
+        <v>0.1211537154453593</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0953878286689681</v>
+        <v>0.1218573242802931</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001274101353094</v>
+        <v>0.0007036088349337</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0938100818360862</v>
+        <v>0.050682899130712</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09390296627179059</v>
+        <v>0.0513831263429593</v>
       </c>
       <c r="D5" t="n">
-        <v>9.288443570439064e-05</v>
+        <v>0.0007002272122473</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1127441452022032</v>
+        <v>0.0957788888064333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1128236273353456</v>
+        <v>0.0961057170822027</v>
       </c>
       <c r="D6" t="n">
-        <v>7.948213314239172e-05</v>
+        <v>0.0003268282757693</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0746291720212407</v>
+        <v>0.0843133943098679</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0746993770181873</v>
+        <v>0.0845074779896217</v>
       </c>
       <c r="D7" t="n">
-        <v>7.020499694659899e-05</v>
+        <v>0.0001940836797538</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0689709772749824</v>
+        <v>0.0830391754619135</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0690269632251086</v>
+        <v>0.08304059726984241</v>
       </c>
       <c r="D8" t="n">
-        <v>5.598595012619445e-05</v>
+        <v>1.421807928905783e-06</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0506485765250824</v>
+        <v>0.0510016261835496</v>
       </c>
       <c r="C9" t="n">
-        <v>0.050682899130712</v>
+        <v>0.0509364015955158</v>
       </c>
       <c r="D9" t="n">
-        <v>3.432260562959838e-05</v>
+        <v>-6.522458803379788e-05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0830637620398518</v>
+        <v>0.0681895381427637</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0830391754619135</v>
+        <v>0.0680987670583674</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.458657793830143e-05</v>
+        <v>-9.077108439629888e-05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0510444832609105</v>
+        <v>0.0690269632251086</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0510016261835496</v>
+        <v>0.0689195103012013</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.285707736090272e-05</v>
+        <v>-0.0001074529239072</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0682346575265034</v>
+        <v>0.09390296627179059</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0681895381427637</v>
+        <v>0.0936182971626163</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.511938373970292e-05</v>
+        <v>-0.0002846691091742</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0843675219547967</v>
+        <v>0.0746993770181873</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0843133943098679</v>
+        <v>0.074301914547207</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.412764492880584e-05</v>
+        <v>-0.0003974624709802</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1212371006723774</v>
+        <v>0.1128236273353456</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1211537154453593</v>
+        <v>0.1123654397155705</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.338522701810402e-05</v>
+        <v>-0.000458187619775</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0959891031523059</v>
+        <v>0.0953878286689681</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0957788888064333</v>
+        <v>0.0948654266546021</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0002102143458725</v>
+        <v>-0.0005224020143659</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3147,19 +3147,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>620.6</v>
+        <v>619.05</v>
       </c>
       <c r="C4" t="n">
-        <v>362.91</v>
+        <v>383.83</v>
       </c>
       <c r="D4" t="n">
-        <v>24.62</v>
+        <v>27.47</v>
       </c>
       <c r="E4" t="n">
-        <v>546.73</v>
+        <v>536.65</v>
       </c>
       <c r="F4" t="n">
-        <v>527.51</v>
+        <v>526.1900000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3179,19 +3179,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>199.41</v>
+        <v>187.23</v>
       </c>
       <c r="C5" t="n">
-        <v>129.5</v>
+        <v>134.31</v>
       </c>
       <c r="D5" t="n">
-        <v>9.960000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="E5" t="n">
-        <v>169.53</v>
+        <v>156.06</v>
       </c>
       <c r="F5" t="n">
-        <v>169.5</v>
+        <v>159.15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>436.9</v>
+        <v>435.8</v>
       </c>
       <c r="C6" t="n">
-        <v>293.22</v>
+        <v>305.04</v>
       </c>
       <c r="D6" t="n">
-        <v>20.77</v>
+        <v>21.87</v>
       </c>
       <c r="E6" t="n">
-        <v>374.59</v>
+        <v>370.2</v>
       </c>
       <c r="F6" t="n">
-        <v>371.36</v>
+        <v>370.43</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9997.5</v>
+        <v>10045</v>
       </c>
       <c r="C7" t="n">
-        <v>8836.360000000001</v>
+        <v>8931.290000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>322.92</v>
+        <v>333.08</v>
       </c>
       <c r="E7" t="n">
-        <v>9028.719999999999</v>
+        <v>9045.780000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>8497.879999999999</v>
+        <v>8538.25</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3275,19 +3275,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1481.8</v>
+        <v>1633.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1030.07</v>
+        <v>1073.54</v>
       </c>
       <c r="D8" t="n">
-        <v>54.65</v>
+        <v>57.21</v>
       </c>
       <c r="E8" t="n">
-        <v>1317.84</v>
+        <v>1461.86</v>
       </c>
       <c r="F8" t="n">
-        <v>1259.53</v>
+        <v>1388.48</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3307,19 +3307,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130.97</v>
+        <v>131.97</v>
       </c>
       <c r="C9" t="n">
-        <v>103.7</v>
+        <v>106.03</v>
       </c>
       <c r="D9" t="n">
-        <v>7.79</v>
+        <v>8.34</v>
       </c>
       <c r="E9" t="n">
-        <v>107.59</v>
+        <v>106.95</v>
       </c>
       <c r="F9" t="n">
-        <v>111.32</v>
+        <v>112.17</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1272</v>
+        <v>1299.3</v>
       </c>
       <c r="C10" t="n">
-        <v>944.22</v>
+        <v>971.48</v>
       </c>
       <c r="D10" t="n">
-        <v>54.13</v>
+        <v>54.63</v>
       </c>
       <c r="E10" t="n">
-        <v>1109.62</v>
+        <v>1135.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1081.2</v>
+        <v>1104.41</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>232.52</v>
+        <v>230.7</v>
       </c>
       <c r="C11" t="n">
-        <v>208.41</v>
+        <v>210.1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.93</v>
+        <v>8.98</v>
       </c>
       <c r="E11" t="n">
-        <v>205.73</v>
+        <v>203.77</v>
       </c>
       <c r="F11" t="n">
-        <v>197.64</v>
+        <v>196.09</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,19 +3403,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.1</v>
+        <v>20.83</v>
       </c>
       <c r="C12" t="n">
-        <v>17.4</v>
+        <v>17.67</v>
       </c>
       <c r="D12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="E12" t="n">
-        <v>17.03</v>
+        <v>17.71</v>
       </c>
       <c r="F12" t="n">
-        <v>17.09</v>
+        <v>17.71</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>512.5</v>
+        <v>521.1</v>
       </c>
       <c r="C13" t="n">
-        <v>460.52</v>
+        <v>465.33</v>
       </c>
       <c r="D13" t="n">
-        <v>24.26</v>
+        <v>24.99</v>
       </c>
       <c r="E13" t="n">
-        <v>439.71</v>
+        <v>446.14</v>
       </c>
       <c r="F13" t="n">
-        <v>435.62</v>
+        <v>442.93</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3467,19 +3467,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>871.8</v>
+        <v>891.4</v>
       </c>
       <c r="C14" t="n">
-        <v>690.1</v>
+        <v>706.48</v>
       </c>
       <c r="D14" t="n">
-        <v>39.4</v>
+        <v>40.54</v>
       </c>
       <c r="E14" t="n">
-        <v>753.61</v>
+        <v>769.79</v>
       </c>
       <c r="F14" t="n">
-        <v>741.03</v>
+        <v>757.6900000000001</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>262.5</v>
+        <v>261.3</v>
       </c>
       <c r="C15" t="n">
-        <v>236.31</v>
+        <v>238.34</v>
       </c>
       <c r="D15" t="n">
-        <v>15.82</v>
+        <v>15.88</v>
       </c>
       <c r="E15" t="n">
-        <v>215.04</v>
+        <v>213.67</v>
       </c>
       <c r="F15" t="n">
-        <v>223.12</v>
+        <v>222.1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 08:08</t>
+          <t>Generated: 2026-06-05 08:36</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1123654397155705</v>
+        <v>0.1123709196121773</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0845074779896217</v>
+        <v>0.08451159516308181</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.074301914547207</v>
+        <v>0.0743055381418856</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1218573242802931</v>
+        <v>0.1218372886682431</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0948654266546021</v>
+        <v>0.0948700531014077</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689195103012013</v>
+        <v>0.068917410225423</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0961057170822027</v>
+        <v>0.0961001296800009</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0680987670583674</v>
+        <v>0.06810012844935449</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0936182971626163</v>
+        <v>0.09362055553069371</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08304059726984241</v>
+        <v>0.0830401848205643</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0513831263429593</v>
+        <v>0.0513853136223861</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0509364015955158</v>
+        <v>0.0509408829847816</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1211537154453593</v>
+        <v>0.1123654397155705</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1218573242802931</v>
+        <v>0.1123709196121773</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007036088349337</v>
+        <v>5.47989660679149e-06</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.050682899130712</v>
+        <v>0.0948654266546021</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0513831263429593</v>
+        <v>0.0948700531014077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007002272122473</v>
+        <v>4.626446805600093e-06</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0957788888064333</v>
+        <v>0.0509364015955158</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0961057170822027</v>
+        <v>0.0509408829847816</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0003268282757693</v>
+        <v>4.481389265800773e-06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0843133943098679</v>
+        <v>0.0845074779896217</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0845074779896217</v>
+        <v>0.08451159516308181</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001940836797538</v>
+        <v>4.117173460105317e-06</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0830391754619135</v>
+        <v>0.074301914547207</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08304059726984241</v>
+        <v>0.0743055381418856</v>
       </c>
       <c r="D8" t="n">
-        <v>1.421807928905783e-06</v>
+        <v>3.623594678606179e-06</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0510016261835496</v>
+        <v>0.0936182971626163</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0509364015955158</v>
+        <v>0.09362055553069371</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.522458803379788e-05</v>
+        <v>2.258368077406869e-06</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0681895381427637</v>
+        <v>0.0513831263429593</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0680987670583674</v>
+        <v>0.0513853136223861</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.077108439629888e-05</v>
+        <v>2.187279426801858e-06</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0690269632251086</v>
+        <v>0.0680987670583674</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0689195103012013</v>
+        <v>0.06810012844935449</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0001074529239072</v>
+        <v>1.361390987095201e-06</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09390296627179059</v>
+        <v>0.08304059726984241</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0936182971626163</v>
+        <v>0.0830401848205643</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0002846691091742</v>
+        <v>-4.124492781060196e-07</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0746993770181873</v>
+        <v>0.0689195103012013</v>
       </c>
       <c r="C13" t="n">
-        <v>0.074301914547207</v>
+        <v>0.068917410225423</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0003974624709802</v>
+        <v>-2.100075778305177e-06</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1128236273353456</v>
+        <v>0.0961057170822027</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1123654397155705</v>
+        <v>0.0961001296800009</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.000458187619775</v>
+        <v>-5.587402201800984e-06</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0953878286689681</v>
+        <v>0.1218573242802931</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0948654266546021</v>
+        <v>0.1218372886682431</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0005224020143659</v>
+        <v>-2.00356120499956e-05</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10045</v>
+        <v>9985</v>
       </c>
       <c r="C7" t="n">
-        <v>8931.290000000001</v>
+        <v>8928.940000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>333.08</v>
+        <v>335.3</v>
       </c>
       <c r="E7" t="n">
-        <v>9045.780000000001</v>
+        <v>8979.1</v>
       </c>
       <c r="F7" t="n">
-        <v>8538.25</v>
+        <v>8487.25</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131.97</v>
+        <v>131.83</v>
       </c>
       <c r="C9" t="n">
         <v>106.03</v>
@@ -3316,10 +3316,10 @@
         <v>8.34</v>
       </c>
       <c r="E9" t="n">
-        <v>106.95</v>
+        <v>106.81</v>
       </c>
       <c r="F9" t="n">
-        <v>112.17</v>
+        <v>112.06</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1299.3</v>
+        <v>1296.2</v>
       </c>
       <c r="C10" t="n">
-        <v>971.48</v>
+        <v>971.36</v>
       </c>
       <c r="D10" t="n">
         <v>54.63</v>
       </c>
       <c r="E10" t="n">
-        <v>1135.4</v>
+        <v>1132.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1104.41</v>
+        <v>1101.77</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>230.7</v>
+        <v>231.38</v>
       </c>
       <c r="C11" t="n">
-        <v>210.1</v>
+        <v>210.12</v>
       </c>
       <c r="D11" t="n">
         <v>8.98</v>
       </c>
       <c r="E11" t="n">
-        <v>203.77</v>
+        <v>204.45</v>
       </c>
       <c r="F11" t="n">
-        <v>196.09</v>
+        <v>196.67</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.83</v>
+        <v>20.8</v>
       </c>
       <c r="C12" t="n">
         <v>17.67</v>
@@ -3412,10 +3412,10 @@
         <v>1.04</v>
       </c>
       <c r="E12" t="n">
-        <v>17.71</v>
+        <v>17.68</v>
       </c>
       <c r="F12" t="n">
-        <v>17.71</v>
+        <v>17.68</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>521.1</v>
+        <v>519.75</v>
       </c>
       <c r="C13" t="n">
-        <v>465.33</v>
+        <v>465.28</v>
       </c>
       <c r="D13" t="n">
         <v>24.99</v>
       </c>
       <c r="E13" t="n">
-        <v>446.14</v>
+        <v>444.79</v>
       </c>
       <c r="F13" t="n">
-        <v>442.93</v>
+        <v>441.79</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>891.4</v>
+        <v>891.25</v>
       </c>
       <c r="C14" t="n">
         <v>706.48</v>
@@ -3476,10 +3476,10 @@
         <v>40.54</v>
       </c>
       <c r="E14" t="n">
-        <v>769.79</v>
+        <v>769.64</v>
       </c>
       <c r="F14" t="n">
-        <v>757.6900000000001</v>
+        <v>757.5599999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>261.3</v>
+        <v>261.8</v>
       </c>
       <c r="C15" t="n">
-        <v>238.34</v>
+        <v>238.36</v>
       </c>
       <c r="D15" t="n">
-        <v>15.88</v>
+        <v>15.9</v>
       </c>
       <c r="E15" t="n">
-        <v>213.67</v>
+        <v>214.09</v>
       </c>
       <c r="F15" t="n">
-        <v>222.1</v>
+        <v>222.53</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 08:36</t>
+          <t>Generated: 2026-06-05 09:04</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1123709196121773</v>
+        <v>0.1123532488123592</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08451159516308181</v>
+        <v>0.0844983053592287</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0743055381418856</v>
+        <v>0.0742938532834327</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1218372886682431</v>
+        <v>0.1218211047885578</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0948700531014077</v>
+        <v>0.09496047992786209</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.068917410225423</v>
+        <v>0.0689231705822993</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0961001296800009</v>
+        <v>0.09609765856233909</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06810012844935449</v>
+        <v>0.0680802413787662</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09362055553069371</v>
+        <v>0.093594484840999</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0830401848205643</v>
+        <v>0.0830382833431713</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0513853136223861</v>
+        <v>0.0514021858545657</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0509408829847816</v>
+        <v>0.0509369832664183</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1123654397155705</v>
+        <v>0.0948700531014077</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1123709196121773</v>
+        <v>0.09496047992786209</v>
       </c>
       <c r="D4" t="n">
-        <v>5.47989660679149e-06</v>
+        <v>9.042682645439561e-05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0948654266546021</v>
+        <v>0.0513853136223861</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0948700531014077</v>
+        <v>0.0514021858545657</v>
       </c>
       <c r="D5" t="n">
-        <v>4.626446805600093e-06</v>
+        <v>1.68722321795961e-05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0509364015955158</v>
+        <v>0.068917410225423</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0509408829847816</v>
+        <v>0.0689231705822993</v>
       </c>
       <c r="D6" t="n">
-        <v>4.481389265800773e-06</v>
+        <v>5.760356876299833e-06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0845074779896217</v>
+        <v>0.0830401848205643</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08451159516308181</v>
+        <v>0.0830382833431713</v>
       </c>
       <c r="D7" t="n">
-        <v>4.117173460105317e-06</v>
+        <v>-1.901477392998729e-06</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.074301914547207</v>
+        <v>0.0961001296800009</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0743055381418856</v>
+        <v>0.09609765856233909</v>
       </c>
       <c r="D8" t="n">
-        <v>3.623594678606179e-06</v>
+        <v>-2.471117661800859e-06</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0936182971626163</v>
+        <v>0.0509408829847816</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09362055553069371</v>
+        <v>0.0509369832664183</v>
       </c>
       <c r="D9" t="n">
-        <v>2.258368077406869e-06</v>
+        <v>-3.899718363301052e-06</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0513831263429593</v>
+        <v>0.0743055381418856</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0513853136223861</v>
+        <v>0.0742938532834327</v>
       </c>
       <c r="D10" t="n">
-        <v>2.187279426801858e-06</v>
+        <v>-1.16848584529039e-05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0680987670583674</v>
+        <v>0.08451159516308181</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06810012844935449</v>
+        <v>0.0844983053592287</v>
       </c>
       <c r="D11" t="n">
-        <v>1.361390987095201e-06</v>
+        <v>-1.328980385310874e-05</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08304059726984241</v>
+        <v>0.1218372886682431</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0830401848205643</v>
+        <v>0.1218211047885578</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.124492781060196e-07</v>
+        <v>-1.618387968529977e-05</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0689195103012013</v>
+        <v>0.1123709196121773</v>
       </c>
       <c r="C13" t="n">
-        <v>0.068917410225423</v>
+        <v>0.1123532488123592</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.100075778305177e-06</v>
+        <v>-1.767079981809805e-05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0961057170822027</v>
+        <v>0.06810012844935449</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0961001296800009</v>
+        <v>0.0680802413787662</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.587402201800984e-06</v>
+        <v>-1.988707058829531e-05</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1218573242802931</v>
+        <v>0.09362055553069371</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1218372886682431</v>
+        <v>0.093594484840999</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.00356120499956e-05</v>
+        <v>-2.607068969470716e-05</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9985</v>
+        <v>9990</v>
       </c>
       <c r="C7" t="n">
-        <v>8928.940000000001</v>
+        <v>8929.139999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>335.3</v>
+        <v>335.88</v>
       </c>
       <c r="E7" t="n">
-        <v>8979.1</v>
+        <v>8982.379999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>8487.25</v>
+        <v>8491.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3275,19 +3275,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1633.5</v>
+        <v>1614.6</v>
       </c>
       <c r="C8" t="n">
-        <v>1073.54</v>
+        <v>1072.8</v>
       </c>
       <c r="D8" t="n">
         <v>57.21</v>
       </c>
       <c r="E8" t="n">
-        <v>1461.86</v>
+        <v>1442.95</v>
       </c>
       <c r="F8" t="n">
-        <v>1388.48</v>
+        <v>1372.41</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3307,19 +3307,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131.83</v>
+        <v>132.27</v>
       </c>
       <c r="C9" t="n">
-        <v>106.03</v>
+        <v>106.05</v>
       </c>
       <c r="D9" t="n">
         <v>8.34</v>
       </c>
       <c r="E9" t="n">
-        <v>106.81</v>
+        <v>107.25</v>
       </c>
       <c r="F9" t="n">
-        <v>112.06</v>
+        <v>112.43</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1296.2</v>
+        <v>1300.3</v>
       </c>
       <c r="C10" t="n">
-        <v>971.36</v>
+        <v>971.52</v>
       </c>
       <c r="D10" t="n">
         <v>54.63</v>
       </c>
       <c r="E10" t="n">
-        <v>1132.3</v>
+        <v>1136.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1101.77</v>
+        <v>1105.26</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>231.38</v>
+        <v>232.9</v>
       </c>
       <c r="C11" t="n">
-        <v>210.12</v>
+        <v>210.18</v>
       </c>
       <c r="D11" t="n">
         <v>8.98</v>
       </c>
       <c r="E11" t="n">
-        <v>204.45</v>
+        <v>205.97</v>
       </c>
       <c r="F11" t="n">
-        <v>196.67</v>
+        <v>197.96</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,19 +3403,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="C12" t="n">
-        <v>17.67</v>
+        <v>17.66</v>
       </c>
       <c r="D12" t="n">
         <v>1.04</v>
       </c>
       <c r="E12" t="n">
-        <v>17.68</v>
+        <v>17.58</v>
       </c>
       <c r="F12" t="n">
-        <v>17.68</v>
+        <v>17.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>519.75</v>
+        <v>523.65</v>
       </c>
       <c r="C13" t="n">
-        <v>465.28</v>
+        <v>465.43</v>
       </c>
       <c r="D13" t="n">
         <v>24.99</v>
       </c>
       <c r="E13" t="n">
-        <v>444.79</v>
+        <v>448.7</v>
       </c>
       <c r="F13" t="n">
-        <v>441.79</v>
+        <v>445.1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3467,19 +3467,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>891.25</v>
+        <v>909.45</v>
       </c>
       <c r="C14" t="n">
-        <v>706.48</v>
+        <v>707.1900000000001</v>
       </c>
       <c r="D14" t="n">
         <v>40.54</v>
       </c>
       <c r="E14" t="n">
-        <v>769.64</v>
+        <v>787.84</v>
       </c>
       <c r="F14" t="n">
-        <v>757.5599999999999</v>
+        <v>773.03</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>261.8</v>
+        <v>263.25</v>
       </c>
       <c r="C15" t="n">
-        <v>238.36</v>
+        <v>238.42</v>
       </c>
       <c r="D15" t="n">
         <v>15.9</v>
       </c>
       <c r="E15" t="n">
-        <v>214.09</v>
+        <v>215.54</v>
       </c>
       <c r="F15" t="n">
-        <v>222.53</v>
+        <v>223.76</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 09:04</t>
+          <t>Generated: 2026-06-05 10:42</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1123532488123592</v>
+        <v>0.112642439159181</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0844983053592287</v>
+        <v>0.0847137374717153</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0742938532834327</v>
+        <v>0.0744832650593469</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1218211047885578</v>
+        <v>0.1220934284878572</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09496047992786209</v>
+        <v>0.0950969670370139</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0689231705822993</v>
+        <v>0.0690761966063477</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09609765856233909</v>
+        <v>0.0940081299136061</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0680802413787662</v>
+        <v>0.0682563070985835</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.093594484840999</v>
+        <v>0.0938008255607557</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0830382833431713</v>
+        <v>0.083240221309926</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0514021858545657</v>
+        <v>0.0515227735564335</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0509369832664183</v>
+        <v>0.0510657087392327</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0948700531014077</v>
+        <v>0.1123532488123592</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09496047992786209</v>
+        <v>0.112642439159181</v>
       </c>
       <c r="D4" t="n">
-        <v>9.042682645439561e-05</v>
+        <v>0.0002891903468218</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0513853136223861</v>
+        <v>0.1218211047885578</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0514021858545657</v>
+        <v>0.1220934284878572</v>
       </c>
       <c r="D5" t="n">
-        <v>1.68722321795961e-05</v>
+        <v>0.0002723236992994</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.068917410225423</v>
+        <v>0.0844983053592287</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0689231705822993</v>
+        <v>0.0847137374717153</v>
       </c>
       <c r="D6" t="n">
-        <v>5.760356876299833e-06</v>
+        <v>0.0002154321124866</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0830401848205643</v>
+        <v>0.093594484840999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0830382833431713</v>
+        <v>0.0938008255607557</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.901477392998729e-06</v>
+        <v>0.0002063407197566</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0961001296800009</v>
+        <v>0.0830382833431713</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09609765856233909</v>
+        <v>0.083240221309926</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.471117661800859e-06</v>
+        <v>0.0002019379667547</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0509408829847816</v>
+        <v>0.0742938532834327</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0509369832664183</v>
+        <v>0.0744832650593469</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.899718363301052e-06</v>
+        <v>0.0001894117759141</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0743055381418856</v>
+        <v>0.0680802413787662</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0742938532834327</v>
+        <v>0.0682563070985835</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.16848584529039e-05</v>
+        <v>0.0001760657198173</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08451159516308181</v>
+        <v>0.0689231705822993</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0844983053592287</v>
+        <v>0.0690761966063477</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.328980385310874e-05</v>
+        <v>0.0001530260240484</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1218372886682431</v>
+        <v>0.09496047992786209</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1218211047885578</v>
+        <v>0.0950969670370139</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.618387968529977e-05</v>
+        <v>0.0001364871091518</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1123709196121773</v>
+        <v>0.0509369832664183</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1123532488123592</v>
+        <v>0.0510657087392327</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.767079981809805e-05</v>
+        <v>0.0001287254728143</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06810012844935449</v>
+        <v>0.0514021858545657</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0680802413787662</v>
+        <v>0.0515227735564335</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.988707058829531e-05</v>
+        <v>0.0001205877018677</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09362055553069371</v>
+        <v>0.09609765856233909</v>
       </c>
       <c r="C15" t="n">
-        <v>0.093594484840999</v>
+        <v>0.0940081299136061</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.607068969470716e-05</v>
+        <v>-0.0020895286487329</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3147,19 +3147,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>619.05</v>
+        <v>619.25</v>
       </c>
       <c r="C4" t="n">
-        <v>383.83</v>
+        <v>383.84</v>
       </c>
       <c r="D4" t="n">
         <v>27.47</v>
       </c>
       <c r="E4" t="n">
-        <v>536.65</v>
+        <v>536.85</v>
       </c>
       <c r="F4" t="n">
-        <v>526.1900000000001</v>
+        <v>526.36</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9990</v>
+        <v>9936.5</v>
       </c>
       <c r="C7" t="n">
-        <v>8929.139999999999</v>
+        <v>8927.040000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>335.88</v>
+        <v>338.28</v>
       </c>
       <c r="E7" t="n">
-        <v>8982.379999999999</v>
+        <v>8921.67</v>
       </c>
       <c r="F7" t="n">
-        <v>8491.5</v>
+        <v>8446.02</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3275,19 +3275,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1614.6</v>
+        <v>1633.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1072.8</v>
+        <v>1073.54</v>
       </c>
       <c r="D8" t="n">
         <v>57.21</v>
       </c>
       <c r="E8" t="n">
-        <v>1442.95</v>
+        <v>1461.86</v>
       </c>
       <c r="F8" t="n">
-        <v>1372.41</v>
+        <v>1388.48</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3307,19 +3307,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132.27</v>
+        <v>131.68</v>
       </c>
       <c r="C9" t="n">
-        <v>106.05</v>
+        <v>106.02</v>
       </c>
       <c r="D9" t="n">
         <v>8.34</v>
       </c>
       <c r="E9" t="n">
-        <v>107.25</v>
+        <v>106.66</v>
       </c>
       <c r="F9" t="n">
-        <v>112.43</v>
+        <v>111.93</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1300.3</v>
+        <v>1202.5</v>
       </c>
       <c r="C10" t="n">
-        <v>971.52</v>
+        <v>967.6900000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>54.63</v>
+        <v>63.27</v>
       </c>
       <c r="E10" t="n">
-        <v>1136.4</v>
+        <v>1012.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1105.26</v>
+        <v>1022.12</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>232.9</v>
+        <v>232.6</v>
       </c>
       <c r="C11" t="n">
-        <v>210.18</v>
+        <v>210.17</v>
       </c>
       <c r="D11" t="n">
         <v>8.98</v>
       </c>
       <c r="E11" t="n">
-        <v>205.97</v>
+        <v>205.67</v>
       </c>
       <c r="F11" t="n">
-        <v>197.96</v>
+        <v>197.71</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20.7</v>
+        <v>20.53</v>
       </c>
       <c r="C12" t="n">
         <v>17.66</v>
@@ -3412,10 +3412,10 @@
         <v>1.04</v>
       </c>
       <c r="E12" t="n">
-        <v>17.58</v>
+        <v>17.41</v>
       </c>
       <c r="F12" t="n">
-        <v>17.6</v>
+        <v>17.45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>523.65</v>
+        <v>532.3</v>
       </c>
       <c r="C13" t="n">
-        <v>465.43</v>
+        <v>465.77</v>
       </c>
       <c r="D13" t="n">
-        <v>24.99</v>
+        <v>25.25</v>
       </c>
       <c r="E13" t="n">
-        <v>448.7</v>
+        <v>456.56</v>
       </c>
       <c r="F13" t="n">
-        <v>445.1</v>
+        <v>452.45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3467,19 +3467,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>909.45</v>
+        <v>899.35</v>
       </c>
       <c r="C14" t="n">
-        <v>707.1900000000001</v>
+        <v>706.79</v>
       </c>
       <c r="D14" t="n">
         <v>40.54</v>
       </c>
       <c r="E14" t="n">
-        <v>787.84</v>
+        <v>777.74</v>
       </c>
       <c r="F14" t="n">
-        <v>773.03</v>
+        <v>764.45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>263.25</v>
+        <v>262.75</v>
       </c>
       <c r="C15" t="n">
-        <v>238.42</v>
+        <v>238.4</v>
       </c>
       <c r="D15" t="n">
         <v>15.9</v>
       </c>
       <c r="E15" t="n">
-        <v>215.54</v>
+        <v>215.04</v>
       </c>
       <c r="F15" t="n">
-        <v>223.76</v>
+        <v>223.34</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 10:42</t>
+          <t>Generated: 2026-06-05 11:08</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.112642439159181</v>
+        <v>0.1126424362700522</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0847137374717153</v>
+        <v>0.08471373529892059</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0744832650593469</v>
+        <v>0.07448326314895019</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1220934284878572</v>
+        <v>0.1220934515591744</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0950969670370139</v>
+        <v>0.09509696459790309</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0690761966063477</v>
+        <v>0.06907619483463499</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0940081299136061</v>
+        <v>0.0940081275024225</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682563070985835</v>
+        <v>0.06825630534789991</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0938008255607557</v>
+        <v>0.0938008231548892</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.083240221309926</v>
+        <v>0.08324021862074441</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0515227735564335</v>
+        <v>0.0515227722349429</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510657087392327</v>
+        <v>0.0510657074294651</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1123532488123592</v>
+        <v>0.1220934284878572</v>
       </c>
       <c r="C4" t="n">
-        <v>0.112642439159181</v>
+        <v>0.1220934515591744</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002891903468218</v>
+        <v>2.307131720391542e-08</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1218211047885578</v>
+        <v>0.0510657087392327</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1220934284878572</v>
+        <v>0.0510657074294651</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002723236992994</v>
+        <v>-1.309767599932954e-09</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0844983053592287</v>
+        <v>0.0515227735564335</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0847137374717153</v>
+        <v>0.0515227722349429</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002154321124866</v>
+        <v>-1.321490597505637e-09</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.093594484840999</v>
+        <v>0.0682563070985835</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0938008255607557</v>
+        <v>0.06825630534789991</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002063407197566</v>
+        <v>-1.750683598089608e-09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0830382833431713</v>
+        <v>0.0690761966063477</v>
       </c>
       <c r="C8" t="n">
-        <v>0.083240221309926</v>
+        <v>0.06907619483463499</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0002019379667547</v>
+        <v>-1.771712707099304e-09</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0742938532834327</v>
+        <v>0.0744832650593469</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0744832650593469</v>
+        <v>0.07448326314895019</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001894117759141</v>
+        <v>-1.910396701942929e-09</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0680802413787662</v>
+        <v>0.0847137374717153</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0682563070985835</v>
+        <v>0.08471373529892059</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001760657198173</v>
+        <v>-2.1727947080441e-09</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0689231705822993</v>
+        <v>0.0938008255607557</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0690761966063477</v>
+        <v>0.0938008231548892</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0001530260240484</v>
+        <v>-2.405866492138919e-09</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09496047992786209</v>
+        <v>0.0940081299136061</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0950969670370139</v>
+        <v>0.0940081275024225</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001364871091518</v>
+        <v>-2.41118360000403e-09</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0509369832664183</v>
+        <v>0.0950969670370139</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0510657087392327</v>
+        <v>0.09509696459790309</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001287254728143</v>
+        <v>-2.439110802221478e-09</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0514021858545657</v>
+        <v>0.083240221309926</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0515227735564335</v>
+        <v>0.08324021862074441</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001205877018677</v>
+        <v>-2.68918159962439e-09</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09609765856233909</v>
+        <v>0.112642439159181</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0940081299136061</v>
+        <v>0.1126424362700522</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0020895286487329</v>
+        <v>-2.889128797312068e-09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 11:08</t>
+          <t>Generated: 2026-06-05 11:56</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1126424362700522</v>
+        <v>0.11264243659416</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08471373529892059</v>
+        <v>0.0847137355426687</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07448326314895019</v>
+        <v>0.074483263363262</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1220934515591744</v>
+        <v>0.122093444679577</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09509696459790309</v>
+        <v>0.095096964871527</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06907619483463499</v>
+        <v>0.0690761993869725</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0940081275024225</v>
+        <v>0.09400812777291349</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06825630534789991</v>
+        <v>0.0682563055442949</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0938008231548892</v>
+        <v>0.0938008234247837</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08324021862074441</v>
+        <v>0.0832402188602528</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0515227722349429</v>
+        <v>0.0515227723831901</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510657074294651</v>
+        <v>0.0510657075763973</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1220934284878572</v>
+        <v>0.06907619483463499</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1220934515591744</v>
+        <v>0.0690761993869725</v>
       </c>
       <c r="D4" t="n">
-        <v>2.307131720391542e-08</v>
+        <v>4.552337506957826e-09</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0510657087392327</v>
+        <v>0.1126424362700522</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0510657074294651</v>
+        <v>0.11264243659416</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.309767599932954e-09</v>
+        <v>3.241077961568806e-10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0515227735564335</v>
+        <v>0.09509696459790309</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0515227722349429</v>
+        <v>0.095096964871527</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.321490597505637e-09</v>
+        <v>2.736239013145791e-10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0682563070985835</v>
+        <v>0.0940081275024225</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06825630534789991</v>
+        <v>0.09400812777291349</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.750683598089608e-09</v>
+        <v>2.70490990716965e-10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0690761966063477</v>
+        <v>0.0938008231548892</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06907619483463499</v>
+        <v>0.0938008234247837</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.771712707099304e-09</v>
+        <v>2.698944956414095e-10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0744832650593469</v>
+        <v>0.08471373529892059</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07448326314895019</v>
+        <v>0.0847137355426687</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.910396701942929e-09</v>
+        <v>2.43748105033248e-10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0847137374717153</v>
+        <v>0.08324021862074441</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08471373529892059</v>
+        <v>0.0832402188602528</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1727947080441e-09</v>
+        <v>2.395083992245972e-10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0938008255607557</v>
+        <v>0.07448326314895019</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0938008231548892</v>
+        <v>0.074483263363262</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.405866492138919e-09</v>
+        <v>2.143118044140024e-10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0940081299136061</v>
+        <v>0.06825630534789991</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0940081275024225</v>
+        <v>0.0682563055442949</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.41118360000403e-09</v>
+        <v>1.96394997487026e-10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0950969670370139</v>
+        <v>0.0515227722349429</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09509696459790309</v>
+        <v>0.0515227723831901</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.439110802221478e-09</v>
+        <v>1.482471992386714e-10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.083240221309926</v>
+        <v>0.0510657074294651</v>
       </c>
       <c r="C14" t="n">
-        <v>0.08324021862074441</v>
+        <v>0.0510657075763973</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.68918159962439e-09</v>
+        <v>1.46932202516048e-10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.112642439159181</v>
+        <v>0.1220934515591744</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1126424362700522</v>
+        <v>0.122093444679577</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.889128797312068e-09</v>
+        <v>-6.879597405640148e-09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 11:56</t>
+          <t>Generated: 2026-06-05 12:02</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.11264243659416</v>
+        <v>0.1126424359339057</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0847137355426687</v>
+        <v>0.0847137309047561</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.074483263363262</v>
+        <v>0.0744832629266779</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.122093444679577</v>
+        <v>0.1220934539667939</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.095096964871527</v>
+        <v>0.0950969643141156</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0690761993869725</v>
+        <v>0.069076198982082</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09400812777291349</v>
+        <v>0.0940081272218843</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0682563055442949</v>
+        <v>0.06825630514421011</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0938008234247837</v>
+        <v>0.0938008228749696</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0832402188602528</v>
+        <v>0.08324021837233971</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0515227723831901</v>
+        <v>0.0515227720811891</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510657075763973</v>
+        <v>0.0510657072770753</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06907619483463499</v>
+        <v>0.122093444679577</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0690761993869725</v>
+        <v>0.1220934539667939</v>
       </c>
       <c r="D4" t="n">
-        <v>4.552337506957826e-09</v>
+        <v>9.287216898301588e-09</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1126424362700522</v>
+        <v>0.0510657075763973</v>
       </c>
       <c r="C5" t="n">
-        <v>0.11264243659416</v>
+        <v>0.0510657072770753</v>
       </c>
       <c r="D5" t="n">
-        <v>3.241077961568806e-10</v>
+        <v>-2.993219977431849e-10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09509696459790309</v>
+        <v>0.0515227723831901</v>
       </c>
       <c r="C6" t="n">
-        <v>0.095096964871527</v>
+        <v>0.0515227720811891</v>
       </c>
       <c r="D6" t="n">
-        <v>2.736239013145791e-10</v>
+        <v>-3.020010005960749e-10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0940081275024225</v>
+        <v>0.0682563055442949</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09400812777291349</v>
+        <v>0.06825630514421011</v>
       </c>
       <c r="D7" t="n">
-        <v>2.70490990716965e-10</v>
+        <v>-4.000847986240785e-10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0938008231548892</v>
+        <v>0.0690761993869725</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0938008234247837</v>
+        <v>0.069076198982082</v>
       </c>
       <c r="D8" t="n">
-        <v>2.698944956414095e-10</v>
+        <v>-4.048904961306832e-10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08471373529892059</v>
+        <v>0.074483263363262</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0847137355426687</v>
+        <v>0.0744832629266779</v>
       </c>
       <c r="D9" t="n">
-        <v>2.43748105033248e-10</v>
+        <v>-4.365841022035966e-10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08324021862074441</v>
+        <v>0.0832402188602528</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0832402188602528</v>
+        <v>0.08324021837233971</v>
       </c>
       <c r="D10" t="n">
-        <v>2.395083992245972e-10</v>
+        <v>-4.879130988122427e-10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07448326314895019</v>
+        <v>0.0938008234247837</v>
       </c>
       <c r="C11" t="n">
-        <v>0.074483263363262</v>
+        <v>0.0938008228749696</v>
       </c>
       <c r="D11" t="n">
-        <v>2.143118044140024e-10</v>
+        <v>-5.49814097028367e-10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06825630534789991</v>
+        <v>0.09400812777291349</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0682563055442949</v>
+        <v>0.0940081272218843</v>
       </c>
       <c r="D12" t="n">
-        <v>1.96394997487026e-10</v>
+        <v>-5.510291944954561e-10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0515227722349429</v>
+        <v>0.095096964871527</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0515227723831901</v>
+        <v>0.0950969643141156</v>
       </c>
       <c r="D13" t="n">
-        <v>1.482471992386714e-10</v>
+        <v>-5.574113948192404e-10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0510657074294651</v>
+        <v>0.11264243659416</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0510657075763973</v>
+        <v>0.1126424359339057</v>
       </c>
       <c r="D14" t="n">
-        <v>1.46932202516048e-10</v>
+        <v>-6.60254295681284e-10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1220934515591744</v>
+        <v>0.0847137355426687</v>
       </c>
       <c r="C15" t="n">
-        <v>0.122093444679577</v>
+        <v>0.0847137309047561</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.879597405640148e-09</v>
+        <v>-4.637912595639726e-09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>

--- a/data/monthly_factsheet.xlsx
+++ b/data/monthly_factsheet.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 12:02</t>
+          <t>Generated: 2026-06-05 12:31</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1126424359339057</v>
+        <v>0.1126424370606531</v>
       </c>
       <c r="C4" t="n">
         <v>17.5</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0847137309047561</v>
+        <v>0.0847137317521364</v>
       </c>
       <c r="C5" t="n">
         <v>15.04</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0744832629266779</v>
+        <v>0.0744832636717242</v>
       </c>
       <c r="C6" t="n">
         <v>15.32</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1220934539667939</v>
+        <v>0.1220934451852102</v>
       </c>
       <c r="C7" t="n">
         <v>11.56</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0950969643141156</v>
+        <v>0.095096965265358</v>
       </c>
       <c r="C8" t="n">
         <v>12.71</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.069076198982082</v>
+        <v>0.0690761996730421</v>
       </c>
       <c r="C9" t="n">
         <v>12.19</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0940081272218843</v>
+        <v>0.0940081281622353</v>
       </c>
       <c r="C10" t="n">
         <v>11.78</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06825630514421011</v>
+        <v>0.068256305826969</v>
       </c>
       <c r="C11" t="n">
         <v>11.33</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0938008228749696</v>
+        <v>0.09380082381324691</v>
       </c>
       <c r="C12" t="n">
         <v>11.04</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08324021837233971</v>
+        <v>0.0832402192049807</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0515227720811891</v>
+        <v>0.0515227725965646</v>
       </c>
       <c r="C14" t="n">
         <v>11.92</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0510657072770753</v>
+        <v>0.0510657077878789</v>
       </c>
       <c r="C15" t="n">
         <v>10.76</v>
@@ -2775,7 +2775,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2817,17 +2817,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.122093444679577</v>
+        <v>0.1126424359339057</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1220934539667939</v>
+        <v>0.1126424370606531</v>
       </c>
       <c r="D4" t="n">
-        <v>9.287216898301588e-09</v>
+        <v>1.126747403712436e-09</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOUTHWEST</t>
+          <t>VENUSREM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0510657075763973</v>
+        <v>0.0950969643141156</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0510657072770753</v>
+        <v>0.095096965265358</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.993219977431849e-10</v>
+        <v>9.512424042901202e-10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2859,17 +2859,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0515227723831901</v>
+        <v>0.0940081272218843</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0515227720811891</v>
+        <v>0.0940081281622353</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.020010005960749e-10</v>
+        <v>9.403510053962449e-10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>GAYAPROJ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0682563055442949</v>
+        <v>0.0938008228749696</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06825630514421011</v>
+        <v>0.09380082381324691</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.000847986240785e-10</v>
+        <v>9.382773030752743e-10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2901,17 +2901,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0690761993869725</v>
+        <v>0.0847137309047561</v>
       </c>
       <c r="C8" t="n">
-        <v>0.069076198982082</v>
+        <v>0.0847137317521364</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.048904961306832e-10</v>
+        <v>8.473802909358951e-10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.074483263363262</v>
+        <v>0.08324021837233971</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0744832629266779</v>
+        <v>0.0832402192049807</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.365841022035966e-10</v>
+        <v>8.326409978165471e-10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0832402188602528</v>
+        <v>0.0744832629266779</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08324021837233971</v>
+        <v>0.0744832636717242</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.879130988122427e-10</v>
+        <v>7.45046302430552e-10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2964,17 +2964,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GAYAPROJ</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0938008234247837</v>
+        <v>0.069076198982082</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0938008228749696</v>
+        <v>0.0690761996730421</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.49814097028367e-10</v>
+        <v>6.90960094695825e-10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2985,17 +2985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.09400812777291349</v>
+        <v>0.06825630514421011</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0940081272218843</v>
+        <v>0.068256305826969</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.510291944954561e-10</v>
+        <v>6.827588910907068e-10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3006,17 +3006,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VENUSREM</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.095096964871527</v>
+        <v>0.0515227720811891</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0950969643141156</v>
+        <v>0.0515227725965646</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.574113948192404e-10</v>
+        <v>5.153754992215376e-10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3027,17 +3027,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SOUTHWEST</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.11264243659416</v>
+        <v>0.0510657072770753</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1126424359339057</v>
+        <v>0.0510657077878789</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.60254295681284e-10</v>
+        <v>5.108036008061312e-10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3048,17 +3048,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0847137355426687</v>
+        <v>0.1220934539667939</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0847137309047561</v>
+        <v>0.1220934451852102</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.637912595639726e-09</v>
+        <v>-8.781583696326756e-09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
